--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 4.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Hotel 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79424A77-A09B-4B0D-BC4D-122B4A8C2500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457A4309-49C3-4A02-9076-C979E6D56A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="4" r:id="rId1"/>
@@ -20,8 +20,39 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -339,6 +370,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -346,27 +396,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -682,38 +713,38 @@
   <sheetData>
     <row r="1" spans="2:14" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
@@ -731,22 +762,22 @@
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="19" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="19" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="12" t="s">
@@ -759,12 +790,12 @@
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="12"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
@@ -780,14 +811,38 @@
       <c r="E6" s="6">
         <v>41096</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="F6" s="9">
+        <f>_xlfn.DAYS(E6,D6)</f>
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f>VLOOKUP(LEFT(B6,2),$B$15:$E$20,2,FALSE)</f>
+        <v>Standart</v>
+      </c>
+      <c r="H6" s="8">
+        <f>IF(VALUE(MID(B6,4,1))=1,VLOOKUP(LEFT(B6,2),$B$15:$E$20,3,FALSE),VLOOKUP(LEFT(B6,2),$B$15:$E$20,4,FALSE))</f>
+        <v>450000</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f>RIGHT(B6,2)</f>
+        <v>01</v>
+      </c>
+      <c r="J6" s="8">
+        <f>F6*H6</f>
+        <v>2250000</v>
+      </c>
+      <c r="K6" s="8">
+        <f>10%*J6</f>
+        <v>225000</v>
+      </c>
+      <c r="L6" s="8" cm="1">
+        <f t="array" ref="L6">_xlfn.IFS(F6&gt;5,4%*J6,F6&lt;=10,4%*J6,F6&gt;10,7%*J6)</f>
+        <v>90000</v>
+      </c>
+      <c r="M6" s="8">
+        <f>J6+K6-L6</f>
+        <v>2385000</v>
+      </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
@@ -802,14 +857,38 @@
       <c r="E7" s="6">
         <v>41101</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="F7" s="9">
+        <f t="shared" ref="F7:F13" si="0">_xlfn.DAYS(E7,D7)</f>
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="str">
+        <f t="shared" ref="G7:G13" si="1">VLOOKUP(LEFT(B7,2),$B$15:$E$20,2,FALSE)</f>
+        <v>G.Tower</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" ref="H7:H13" si="2">IF(VALUE(MID(B7,4,1))=1,VLOOKUP(LEFT(B7,2),$B$15:$E$20,3,FALSE),VLOOKUP(LEFT(B7,2),$B$15:$E$20,4,FALSE))</f>
+        <v>315000</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f t="shared" ref="I7:I13" si="3">RIGHT(B7,2)</f>
+        <v>08</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" ref="J7:J13" si="4">F7*H7</f>
+        <v>3150000</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" ref="K7:K13" si="5">10%*J7</f>
+        <v>315000</v>
+      </c>
+      <c r="L7" s="8" cm="1">
+        <f t="array" ref="L7">_xlfn.IFS(F7&gt;5,4%*J7,F7&lt;=10,4%*J7,F7&gt;10,7%*J7)</f>
+        <v>126000</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" ref="M7:M13" si="6">J7+K7-L7</f>
+        <v>3339000</v>
+      </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
@@ -824,14 +903,38 @@
       <c r="E8" s="6">
         <v>41114</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="F8" s="9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Weel</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="2"/>
+        <v>400000</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>02</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="4"/>
+        <v>7200000</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="5"/>
+        <v>720000</v>
+      </c>
+      <c r="L8" s="8" cm="1">
+        <f t="array" ref="L8">_xlfn.IFS(F8&gt;5,4%*J8,F8&lt;=10,4%*J8,F8&gt;10,7%*J8)</f>
+        <v>288000</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" si="6"/>
+        <v>7632000</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
@@ -846,14 +949,38 @@
       <c r="E9" s="6">
         <v>41105</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="F9" s="9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G9" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>VIP Class</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="2"/>
+        <v>399000</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>07</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="4"/>
+        <v>3192000</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="5"/>
+        <v>319200</v>
+      </c>
+      <c r="L9" s="8" cm="1">
+        <f t="array" ref="L9">_xlfn.IFS(F9&gt;5,4%*J9,F9&lt;=10,4%*J9,F9&gt;10,7%*J9)</f>
+        <v>127680</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" si="6"/>
+        <v>3383520</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -868,14 +995,38 @@
       <c r="E10" s="6">
         <v>41100</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="F10" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>G.Tower</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="2"/>
+        <v>485000</v>
+      </c>
+      <c r="I10" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>05</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="4"/>
+        <v>970000</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="5"/>
+        <v>97000</v>
+      </c>
+      <c r="L10" s="8" cm="1">
+        <f t="array" ref="L10">_xlfn.IFS(F10&gt;5,4%*J10,F10&lt;=10,4%*J10,F10&gt;10,7%*J10)</f>
+        <v>38800</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" si="6"/>
+        <v>1028200</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -890,14 +1041,38 @@
       <c r="E11" s="6">
         <v>41110</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="F11" s="9">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G11" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Weel</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="2"/>
+        <v>400000</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>06</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="4"/>
+        <v>4800000</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="5"/>
+        <v>480000</v>
+      </c>
+      <c r="L11" s="8" cm="1">
+        <f t="array" ref="L11">_xlfn.IFS(F11&gt;5,4%*J11,F11&lt;=10,4%*J11,F11&gt;10,7%*J11)</f>
+        <v>192000</v>
+      </c>
+      <c r="M11" s="8">
+        <f t="shared" si="6"/>
+        <v>5088000</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
@@ -912,14 +1087,38 @@
       <c r="E12" s="6">
         <v>41107</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="F12" s="9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G12" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>VIP Class</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="2"/>
+        <v>399000</v>
+      </c>
+      <c r="I12" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>04</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="4"/>
+        <v>2793000</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" si="5"/>
+        <v>279300</v>
+      </c>
+      <c r="L12" s="8" cm="1">
+        <f t="array" ref="L12">_xlfn.IFS(F12&gt;5,4%*J12,F12&lt;=10,4%*J12,F12&gt;10,7%*J12)</f>
+        <v>111720</v>
+      </c>
+      <c r="M12" s="8">
+        <f t="shared" si="6"/>
+        <v>2960580</v>
+      </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
@@ -934,40 +1133,64 @@
       <c r="E13" s="6">
         <v>41103</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="F13" s="9">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G13" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>Standart</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="2"/>
+        <v>450000</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>09</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="4"/>
+        <v>1350000</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="5"/>
+        <v>135000</v>
+      </c>
+      <c r="L13" s="8" cm="1">
+        <f t="array" ref="L13">_xlfn.IFS(F13&gt;5,4%*J13,F13&lt;=10,4%*J13,F13&gt;10,7%*J13)</f>
+        <v>54000</v>
+      </c>
+      <c r="M13" s="8">
+        <f t="shared" si="6"/>
+        <v>1431000</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="14"/>
       <c r="G15" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="10" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1033,121 +1256,134 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="14"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="M4:M5"/>
@@ -1163,19 +1399,6 @@
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G16" r:id="rId1" xr:uid="{D5015FA4-93CE-4E3D-8B98-B22D5991DACB}"/>
